--- a/artfynd/A 20914-2026 artfynd.xlsx
+++ b/artfynd/A 20914-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134422500</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>134422424</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20914-2026 artfynd.xlsx
+++ b/artfynd/A 20914-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134422500</v>
+        <v>134422424</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677723</v>
+        <v>677726</v>
       </c>
       <c r="R2" t="n">
-        <v>6617193</v>
+        <v>6617201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134422424</v>
+        <v>134422500</v>
       </c>
       <c r="B3" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677726</v>
+        <v>677723</v>
       </c>
       <c r="R3" t="n">
-        <v>6617201</v>
+        <v>6617193</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
